--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-view-for-type.xlsx
+++ b/fhir/ValueSet-ehealth-view-for-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
